--- a/communities_hubs_brongestuurd.xlsx
+++ b/communities_hubs_brongestuurd.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -84,6 +84,11 @@
     <font>
       <name val="Arial"/>
       <color rgb="00CC0000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -196,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -368,6 +373,24 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -735,7 +758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2021,11 +2044,10 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="42" customHeight="1">
+    <row r="23" ht="18" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>21 energiehubs Noord-Holland
-(namen niet publiek vermeld)</t>
+          <t>Alton</t>
         </is>
       </c>
       <c r="B23" s="25" t="inlineStr">
@@ -2038,464 +2060,1704 @@
           <t>BT-energiehub</t>
         </is>
       </c>
-      <c r="D23" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H23" s="27" t="inlineStr">
+      <c r="D23" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="60" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="I23" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J23" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K23" s="28" t="inlineStr">
-        <is>
-          <t>🔓</t>
-        </is>
-      </c>
-      <c r="L23" s="9" t="inlineStr">
-        <is>
-          <t>Noord-holland.nl mei 2025: '21 energiehubs ondersteund'
-Selectiecriteria: middenspanningscongestietoets Liander; namen individuele hubs niet gepubliceerd</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="42" customHeight="1">
-      <c r="A24" s="29" t="inlineStr">
+      <c r="I23" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K23" s="61" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L23" s="62" t="inlineStr">
+        <is>
+          <t>energieregionh.nl/media/.../deelnemers-stimuleringsprogramma-energiehubs.pdf (23 jun 2025) | gemeente: Dijk en Waard | Fase 1: Verkennen</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>Baanstee Noord</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="C24" s="25" t="inlineStr">
+        <is>
+          <t>BT-energiehub</t>
+        </is>
+      </c>
+      <c r="D24" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I24" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J24" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K24" s="61" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L24" s="62" t="inlineStr">
+        <is>
+          <t>energieregionh.nl/media/.../deelnemers-stimuleringsprogramma-energiehubs.pdf (23 jun 2025) | gemeente: Purmerend | Fase 1: Verkennen</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>De Grote Hout</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="C25" s="25" t="inlineStr">
+        <is>
+          <t>BT-energiehub</t>
+        </is>
+      </c>
+      <c r="D25" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I25" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K25" s="61" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L25" s="62" t="inlineStr">
+        <is>
+          <t>energieregionh.nl/media/.../deelnemers-stimuleringsprogramma-energiehubs.pdf (23 jun 2025) | gemeente: Velsen | Fase 1: Verkennen</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>De Veken</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="C26" s="25" t="inlineStr">
+        <is>
+          <t>BT-energiehub</t>
+        </is>
+      </c>
+      <c r="D26" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I26" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J26" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K26" s="61" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L26" s="62" t="inlineStr">
+        <is>
+          <t>energieregionh.nl/media/.../deelnemers-stimuleringsprogramma-energiehubs.pdf (23 jun 2025) | gemeente: Opmeer | Fase 1: Verkennen</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Het Grootslag</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="C27" s="25" t="inlineStr">
+        <is>
+          <t>BT-energiehub</t>
+        </is>
+      </c>
+      <c r="D27" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I27" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J27" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K27" s="61" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L27" s="62" t="inlineStr">
+        <is>
+          <t>energieregionh.nl/media/.../deelnemers-stimuleringsprogramma-energiehubs.pdf (23 jun 2025) | gemeente: Medemblik | Fase 1: Verkennen</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>HoogTij</t>
+        </is>
+      </c>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="C28" s="25" t="inlineStr">
+        <is>
+          <t>BT-energiehub</t>
+        </is>
+      </c>
+      <c r="D28" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H28" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I28" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J28" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K28" s="61" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L28" s="62" t="inlineStr">
+        <is>
+          <t>energieregionh.nl/media/.../deelnemers-stimuleringsprogramma-energiehubs.pdf (23 jun 2025) | gemeente: Zaanstad | Fase 1: Verkennen</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Kooypunt</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="C29" s="25" t="inlineStr">
+        <is>
+          <t>BT-energiehub</t>
+        </is>
+      </c>
+      <c r="D29" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I29" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J29" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K29" s="61" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L29" s="62" t="inlineStr">
+        <is>
+          <t>energieregionh.nl/media/.../deelnemers-stimuleringsprogramma-energiehubs.pdf (23 jun 2025) | gemeente: Den Helder | Fase 1: Verkennen</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Loswalcluster</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="C30" s="25" t="inlineStr">
+        <is>
+          <t>BT-energiehub</t>
+        </is>
+      </c>
+      <c r="D30" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I30" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J30" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K30" s="61" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L30" s="62" t="inlineStr">
+        <is>
+          <t>energieregionh.nl/media/.../deelnemers-stimuleringsprogramma-energiehubs.pdf (23 jun 2025) | gemeente: Hilversum | Fase 1: Verkennen</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Smart Grid Haven Den Helder</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="inlineStr">
+        <is>
+          <t>BT-energiehub</t>
+        </is>
+      </c>
+      <c r="D31" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I31" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K31" s="61" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L31" s="62" t="inlineStr">
+        <is>
+          <t>energieregionh.nl/media/.../deelnemers-stimuleringsprogramma-energiehubs.pdf (23 jun 2025) | gemeente: Den Helder | Fase 1: Verkennen</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Gooimeer</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="C32" s="25" t="inlineStr">
+        <is>
+          <t>BT-energiehub</t>
+        </is>
+      </c>
+      <c r="D32" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H32" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I32" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J32" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K32" s="61" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L32" s="62" t="inlineStr">
+        <is>
+          <t>energieregionh.nl/media/.../deelnemers-stimuleringsprogramma-energiehubs.pdf (23 jun 2025) | gemeente: Gooische Meren | Fase 1: Verkennen</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Hoorn80</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="C33" s="25" t="inlineStr">
+        <is>
+          <t>BT-energiehub</t>
+        </is>
+      </c>
+      <c r="D33" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I33" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J33" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K33" s="61" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L33" s="62" t="inlineStr">
+        <is>
+          <t>energieregionh.nl/media/.../deelnemers-stimuleringsprogramma-energiehubs.pdf (23 jun 2025) | gemeente: Hoorn | Fase 1: Verkennen</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Zuiderdel</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="C34" s="25" t="inlineStr">
+        <is>
+          <t>BT-energiehub</t>
+        </is>
+      </c>
+      <c r="D34" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H34" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I34" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J34" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K34" s="61" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L34" s="62" t="inlineStr">
+        <is>
+          <t>energieregionh.nl/media/.../deelnemers-stimuleringsprogramma-energiehubs.pdf (23 jun 2025) | gemeente: Dijk en Waard | Fase 1: Verkennen</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Beverkoog</t>
+        </is>
+      </c>
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="C35" s="25" t="inlineStr">
+        <is>
+          <t>BT-energiehub</t>
+        </is>
+      </c>
+      <c r="D35" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H35" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I35" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J35" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K35" s="61" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L35" s="62" t="inlineStr">
+        <is>
+          <t>energieregionh.nl/media/.../deelnemers-stimuleringsprogramma-energiehubs.pdf (23 jun 2025) | gemeente: Alkmaar | Fase 1: Verkennen</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>ArenApoort</t>
+        </is>
+      </c>
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="C36" s="25" t="inlineStr">
+        <is>
+          <t>BT-energiehub</t>
+        </is>
+      </c>
+      <c r="D36" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I36" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J36" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K36" s="61" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L36" s="62" t="inlineStr">
+        <is>
+          <t>energieregionh.nl/media/.../deelnemers-stimuleringsprogramma-energiehubs.pdf (23 jun 2025) | gemeente: Amsterdam | Fase 2: Plannen &amp; Ontwerpen</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Beverwijk Business Docks</t>
+        </is>
+      </c>
+      <c r="B37" s="25" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="C37" s="25" t="inlineStr">
+        <is>
+          <t>BT-energiehub</t>
+        </is>
+      </c>
+      <c r="D37" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I37" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J37" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K37" s="61" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L37" s="62" t="inlineStr">
+        <is>
+          <t>energieregionh.nl/media/.../deelnemers-stimuleringsprogramma-energiehubs.pdf (23 jun 2025) | gemeente: Beverwijk | Fase 2: Plannen &amp; Ontwerpen</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>Havengebied Ijmuiden</t>
+        </is>
+      </c>
+      <c r="B38" s="25" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="C38" s="25" t="inlineStr">
+        <is>
+          <t>BT-energiehub</t>
+        </is>
+      </c>
+      <c r="D38" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I38" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J38" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K38" s="61" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L38" s="62" t="inlineStr">
+        <is>
+          <t>energieregionh.nl/media/.../deelnemers-stimuleringsprogramma-energiehubs.pdf (23 jun 2025) | gemeente: Velsen | Fase 2: Plannen &amp; Ontwerpen</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>Nieuw-Vennep Zuid</t>
+        </is>
+      </c>
+      <c r="B39" s="25" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="C39" s="25" t="inlineStr">
+        <is>
+          <t>BT-energiehub</t>
+        </is>
+      </c>
+      <c r="D39" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I39" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J39" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K39" s="61" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L39" s="62" t="inlineStr">
+        <is>
+          <t>energieregionh.nl/media/.../deelnemers-stimuleringsprogramma-energiehubs.pdf (23 jun 2025) | gemeente: Haarlemmermeer | Fase 2: Plannen &amp; Ontwerpen</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>Polanenpark</t>
+        </is>
+      </c>
+      <c r="B40" s="25" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="C40" s="25" t="inlineStr">
+        <is>
+          <t>BT-energiehub</t>
+        </is>
+      </c>
+      <c r="D40" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I40" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J40" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K40" s="61" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L40" s="62" t="inlineStr">
+        <is>
+          <t>energieregionh.nl/media/.../deelnemers-stimuleringsprogramma-energiehubs.pdf (23 jun 2025) | gemeente: Haarlemmermeer | Fase 2: Plannen &amp; Ontwerpen</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>Project Doen-2 / Noorderveld Wormerveer</t>
+        </is>
+      </c>
+      <c r="B41" s="25" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="C41" s="25" t="inlineStr">
+        <is>
+          <t>BT-energiehub</t>
+        </is>
+      </c>
+      <c r="D41" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E41" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I41" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J41" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K41" s="61" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L41" s="62" t="inlineStr">
+        <is>
+          <t>energieregionh.nl/media/.../deelnemers-stimuleringsprogramma-energiehubs.pdf (23 jun 2025) | gemeente: Zaanstad | Fase 2: Plannen &amp; Ontwerpen</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>Westfrisia</t>
+        </is>
+      </c>
+      <c r="B42" s="25" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="C42" s="25" t="inlineStr">
+        <is>
+          <t>BT-energiehub</t>
+        </is>
+      </c>
+      <c r="D42" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E42" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I42" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J42" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K42" s="61" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L42" s="62" t="inlineStr">
+        <is>
+          <t>energieregionh.nl/media/.../deelnemers-stimuleringsprogramma-energiehubs.pdf (23 jun 2025) | gemeente: Hoorn | Fase 2: Plannen &amp; Ontwerpen</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>Waarderpolder</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="inlineStr">
+        <is>
+          <t>Noord-Holland</t>
+        </is>
+      </c>
+      <c r="C43" s="25" t="inlineStr">
+        <is>
+          <t>BT-energiehub</t>
+        </is>
+      </c>
+      <c r="D43" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I43" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J43" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K43" s="61" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L43" s="62" t="inlineStr">
+        <is>
+          <t>energieregionh.nl/media/.../deelnemers-stimuleringsprogramma-energiehubs.pdf (23 jun 2025) | gemeente: Haarlem | Fase 2: Plannen &amp; Ontwerpen</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="29" t="inlineStr">
         <is>
           <t>Schiphol Trade Park (operationeel, 7 bedrijven)
 – in NH-programma-regio</t>
         </is>
       </c>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B44" s="30" t="inlineStr">
         <is>
           <t>Noord-Holland</t>
         </is>
       </c>
-      <c r="C24" s="30" t="inlineStr">
+      <c r="C44" s="30" t="inlineStr">
         <is>
           <t>BT-energiehub</t>
         </is>
       </c>
-      <c r="D24" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F24" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H24" s="32" t="inlineStr">
+      <c r="D44" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="32" t="inlineStr">
         <is>
           <t>❓</t>
         </is>
       </c>
-      <c r="I24" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J24" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K24" s="33" t="inlineStr">
-        <is>
-          <t>🔓</t>
-        </is>
-      </c>
-      <c r="L24" s="9" t="inlineStr">
+      <c r="I44" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J44" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K44" s="33" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L44" s="9" t="inlineStr">
         <is>
           <t>Kamerstuk 32813-1398: 'eerste echte energiehub NL'; of NH-subsidie ontvangen: NIET bevestigd in bron</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="34" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="34" t="inlineStr">
         <is>
           <t>EWB CoP Brabant
 – deelnemers achter login, niet publiek</t>
         </is>
       </c>
-      <c r="B25" s="35" t="inlineStr">
+      <c r="B45" s="35" t="inlineStr">
         <is>
           <t>Noord-Brabant</t>
         </is>
       </c>
-      <c r="C25" s="35" t="inlineStr">
+      <c r="C45" s="35" t="inlineStr">
         <is>
           <t>BT-energiehub</t>
         </is>
       </c>
-      <c r="D25" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E25" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F25" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G25" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H25" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I25" s="37" t="inlineStr">
+      <c r="D45" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" s="37" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="J25" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K25" s="38" t="inlineStr">
-        <is>
-          <t>🔓</t>
-        </is>
-      </c>
-      <c r="L25" s="9" t="inlineStr">
+      <c r="J45" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K45" s="38" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="inlineStr">
         <is>
           <t>EWB: 'pagina in ontwikkeling; toegang via ledenlogin'; deelnemers niet publiek</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="29" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="29" t="inlineStr">
         <is>
           <t>KBP Hapert (operationeel, 5 bedrijven + Tibo Energy)
 – in Brabant-regio, CoP-lid: niet bevestigd</t>
         </is>
       </c>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="B46" s="30" t="inlineStr">
         <is>
           <t>Noord-Brabant</t>
         </is>
       </c>
-      <c r="C26" s="30" t="inlineStr">
+      <c r="C46" s="30" t="inlineStr">
         <is>
           <t>BT-energiehub</t>
         </is>
       </c>
-      <c r="D26" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E26" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H26" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I26" s="32" t="inlineStr">
+      <c r="D46" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" s="32" t="inlineStr">
         <is>
           <t>❓</t>
         </is>
       </c>
-      <c r="J26" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K26" s="33" t="inlineStr">
-        <is>
-          <t>🔓</t>
-        </is>
-      </c>
-      <c r="L26" s="9" t="inlineStr">
+      <c r="J46" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K46" s="33" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L46" s="9" t="inlineStr">
         <is>
           <t>EWB kennisthema: vermeld als 'voorbeeld energiehub Brabant'; CoP-lid: niet bevestigd in bron</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="42" customHeight="1">
-      <c r="A27" s="39" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="39" t="inlineStr">
         <is>
           <t>ZH CoP (SSF)
 – deelnemers niet publiek gepubliceerd</t>
         </is>
       </c>
-      <c r="B27" s="40" t="inlineStr">
+      <c r="B47" s="40" t="inlineStr">
         <is>
           <t>Zuid-Holland</t>
         </is>
       </c>
-      <c r="C27" s="40" t="inlineStr">
+      <c r="C47" s="40" t="inlineStr">
         <is>
           <t>BT-energiehub</t>
         </is>
       </c>
-      <c r="D27" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E27" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F27" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G27" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H27" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I27" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J27" s="42" t="inlineStr">
+      <c r="D47" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I47" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J47" s="42" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="K27" s="43" t="inlineStr">
-        <is>
-          <t>🔓</t>
-        </is>
-      </c>
-      <c r="L27" s="9" t="inlineStr">
+      <c r="K47" s="43" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L47" s="9" t="inlineStr">
         <is>
           <t>Sustainablescale-up.com: 5 CoPs dec 2024–nov 2025; deelnemende hubs niet bij naam gepubliceerd
 Doelgroep: bedrijven, gemeenten, adviesbureaus, netbeheerders ZH</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="42" customHeight="1">
-      <c r="A28" s="29" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="29" t="inlineStr">
         <is>
           <t>Energiehub Lage Weide Utrecht
 – in ZH-regio? Nee, maar als PVB-lanceringsvoorbeeld</t>
         </is>
       </c>
-      <c r="B28" s="30" t="inlineStr">
+      <c r="B48" s="30" t="inlineStr">
         <is>
           <t>Utrecht</t>
         </is>
       </c>
-      <c r="C28" s="30" t="inlineStr">
+      <c r="C48" s="30" t="inlineStr">
         <is>
           <t>BT-energiehub</t>
         </is>
       </c>
-      <c r="D28" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E28" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F28" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G28" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H28" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I28" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J28" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K28" s="33" t="inlineStr">
-        <is>
-          <t>🔓</t>
-        </is>
-      </c>
-      <c r="L28" s="9" t="inlineStr">
+      <c r="D48" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E48" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I48" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J48" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K48" s="33" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L48" s="9" t="inlineStr">
         <is>
           <t>PVB-lancering kennisplatform: 'Lage Weide maakt efficiënter gebruik van energienet'
 Geen ZH CoP-deelname bevestigd</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="42" customHeight="1">
-      <c r="A29" s="44" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="44" t="inlineStr">
         <is>
           <t>Kennisplatform energiehubs.nl
 (63+ initiatieven, zelfregistratie-radar)</t>
         </is>
       </c>
-      <c r="B29" s="45" t="inlineStr">
+      <c r="B49" s="45" t="inlineStr">
         <is>
           <t>Landelijk</t>
         </is>
       </c>
-      <c r="C29" s="45" t="inlineStr">
+      <c r="C49" s="45" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D29" s="46" t="inlineStr">
-        <is>
-          <t>🔓</t>
-        </is>
-      </c>
-      <c r="E29" s="46" t="inlineStr">
-        <is>
-          <t>🔓</t>
-        </is>
-      </c>
-      <c r="F29" s="47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="46" t="inlineStr">
-        <is>
-          <t>🔓</t>
-        </is>
-      </c>
-      <c r="H29" s="46" t="inlineStr">
-        <is>
-          <t>🔓</t>
-        </is>
-      </c>
-      <c r="I29" s="46" t="inlineStr">
-        <is>
-          <t>🔓</t>
-        </is>
-      </c>
-      <c r="J29" s="46" t="inlineStr">
-        <is>
-          <t>🔓</t>
-        </is>
-      </c>
-      <c r="K29" s="46" t="inlineStr">
-        <is>
-          <t>🔓</t>
-        </is>
-      </c>
-      <c r="L29" s="9" t="inlineStr">
+      <c r="D49" s="46" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="E49" s="46" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="F49" s="47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="46" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="H49" s="46" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="I49" s="46" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="J49" s="46" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="K49" s="46" t="inlineStr">
+        <is>
+          <t>🔓</t>
+        </is>
+      </c>
+      <c r="L49" s="9" t="inlineStr">
         <is>
           <t>Energiehubs.nl: open platform, geen vaste leden; ieder initiatief kan zich aanmelden
 Beheer per dec 2025 overgedragen van netbeheerders aan PVB Nederland</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="48" t="inlineStr">
+    <row r="50"/>
+    <row r="51">
+      <c r="A51" s="48" t="inlineStr">
         <is>
           <t>LEGENDA</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="49" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">   ✅  Aantoonbare deelname – expliciet vermeld in publieke bron (website, persbericht, intentieovereenkomst)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="49" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">   ❓  Niet te bevestigen – hub ligt in regio, maar deelname aan community niet bevestigd in bron</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="49" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">   🔓  Open platform – ieder initiatief kan zichzelf aanmelden, geen vaste lidmaatschapslijst</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="49" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">   —  Niet van toepassing – community is niet actief in dit type of deze regio</t>
         </is>
@@ -2715,7 +3977,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="90" customHeight="1">
+    <row r="7" ht="160" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
           <t>Stimuleringsprogramma Energiehubs
@@ -2732,21 +3994,42 @@
           <t>BT-energiehubs</t>
         </is>
       </c>
-      <c r="D7" s="52" t="inlineStr">
-        <is>
-          <t>NEE – aantal bekend, namen niet</t>
-        </is>
-      </c>
-      <c r="E7" s="25" t="inlineStr">
-        <is>
-          <t>Noord-holland.nl mei 2025: '21 energiehubs ondersteund, €50K–60K per stuk'.
-Selectiecriterium: middenspanningscongestietoets Liander.
-Bron: Noord-Holland.nl.</t>
-        </is>
-      </c>
-      <c r="F7" s="25" t="inlineStr">
-        <is>
-          <t>Namen van de 21 gehonoreerde initiatieven niet gepubliceerd. 2e ronde aangekondigd voor 2026.</t>
+      <c r="D7" s="63" t="inlineStr">
+        <is>
+          <t>JA – 21 hubs bij naam bekend</t>
+        </is>
+      </c>
+      <c r="E7" s="64" t="inlineStr">
+        <is>
+          <t>Bron: energieregionh.nl/media/.../deelnemers-stimuleringsprogramma-energiehubs.pdf (23 jun 2025)
+Fase 1 – Verkennen (13 hubs):
+• Alton (Dijk en Waard)
+• Baanstee Noord (Purmerend)
+• De Grote Hout (Velsen)
+• De Veken (Opmeer)
+• Het Grootslag (Medemblik)
+• HoogTij (Zaanstad)
+• Kooypunt (Den Helder)
+• Loswalcluster (Hilversum)
+• Smart Grid Haven Den Helder (Den Helder)
+• Gooimeer (Gooische Meren)
+• Hoorn80 (Hoorn)
+• Zuiderdel (Dijk en Waard)
+• Beverkoog (Alkmaar)
+Fase 2 – Plannen &amp; Ontwerpen (8 hubs):
+• ArenApoort (Amsterdam)
+• Beverwijk Business Docks (Beverwijk)
+• Havengebied Ijmuiden (Velsen)
+• Nieuw-Vennep Zuid (Haarlemmermeer)
+• Polanenpark (Haarlemmermeer)
+• Project Doen-2 / Noorderveld Wormerveer (Zaanstad)
+• Westfrisia (Hoorn)
+• Waarderpolder (Haarlem)</t>
+        </is>
+      </c>
+      <c r="F7" s="62" t="inlineStr">
+        <is>
+          <t>Hubregisseur voor 5 hubs nog niet ingevuld (–). Polanenpark: onzeker of hub doorgaat. 2e ronde stimuleringsprogramma aangekondigd voor 2026.</t>
         </is>
       </c>
     </row>
@@ -3029,12 +4312,12 @@
       </c>
       <c r="B10" s="57" t="inlineStr">
         <is>
-          <t>https://www.noord-holland.nl/.../Provincie_Noord_Holland_ondersteunt_21_energiehubs</t>
+          <t>https://energieregionh.nl/media/pages/medialibrary/ac59ab6032-1759474597/deelnemers-stimuleringsprogramma-energiehubs.pdf</t>
         </is>
       </c>
       <c r="C10" s="57" t="inlineStr">
         <is>
-          <t>Gemiddeld – 21 hubs bevestigd, namen niet gepubliceerd</t>
+          <t>Hoog – 21 deelnemers bij naam, per fase en gemeente (23 jun 2025)</t>
         </is>
       </c>
     </row>
